--- a/Assets/Data/DataTable/09_Element_Status.xlsx
+++ b/Assets/Data/DataTable/09_Element_Status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84EFE38-A7E0-41F4-A28F-D2B0C0D04B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E690A0-A3AC-43E3-91C4-0BBF4D2C5827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -374,7 +374,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="90">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -718,10 +718,6 @@
   </si>
   <si>
     <t>상한 하한</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상태 이상, 버프 디버프 같이할지 말지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3841,9 +3837,7 @@
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
       <c r="H5" s="25"/>
-      <c r="I5" s="25" t="s">
-        <v>90</v>
-      </c>
+      <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
       <c r="L5" s="25"/>

--- a/Assets/Data/DataTable/09_Element_Status.xlsx
+++ b/Assets/Data/DataTable/09_Element_Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E690A0-A3AC-43E3-91C4-0BBF4D2C5827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D130599-E440-456B-94AD-7F93C13F8068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -344,29 +344,1415 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={E8D9F2FE-E5E0-40C4-A56A-56D345786A22}</author>
+    <author>제동우</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{E8D9F2FE-E5E0-40C4-A56A-56D345786A22}">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{F39414A5-AD79-44F4-8E5B-6901F30712C2}">
       <text>
-        <t xml:space="preserve">[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    0: None
-1: 물리
-2: 화염
-3: 방사능
-4: 중력
-5: 공허
-6: 신성
-7: 물리+물리
-8: 화염+화염
-9: 방사능+방사능
-10: 중력+중력
-11: 공허+공허
-12: 신성+신성
-13: 카오스
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0: None
+1: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>단일</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>속성</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>중첩</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>-</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>동일</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">속성
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>서로</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>다른</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>속성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{126D906A-781A-4BA9-8A8E-7F63B254B92C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">0: NONE
+1: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">기절
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>매턴</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">데미지
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3: SP </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>소모량</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">증가
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">4: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>스피드</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">감소
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">5: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>타겟</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>랜덤</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">지정
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">6: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>스킬</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">잠금
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">7: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>매턴</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>데미지</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>데미지</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">증가
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">8: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>공격</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>행동</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>아군</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>대상</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">지정
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">9: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>속성</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>게이지</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>저항</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>감소</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{B0B74666-F72C-41F1-BE61-ADD7D16A76DF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>디버프가</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>필요한</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>경우</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기입
+필요</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>없는</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>경우</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> "-" </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기입</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{C2095F88-B0F9-4F1B-B152-8ADD4BD51B2D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">물리
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">2: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">화염
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">3: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">방사능
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">4: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">중력
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">5: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">공허
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">6: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">신성
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>7: (</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>물리</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>물리</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>8: (</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>화염</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>화염</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>9: (</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>방사능</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>방사능</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>10: (</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>중력</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>중력</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>11: (</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>공허</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>공허</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>12: (</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신성</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신성</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">13: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">카오스
+</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -374,7 +1760,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="94">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -679,10 +2065,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Element_Status_Table</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>enum:RANGE_TYPE:NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -691,33 +2073,54 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>enum:category</t>
-  </si>
-  <si>
-    <t>enum:category</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Element_Status_Category</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>상태 이상 카테고리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>지속 턴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>변화 스탯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상한 하한</t>
+    <t>enum:Element_Status_Category:NONE</t>
+  </si>
+  <si>
+    <t>enum:Element_Status_Category:NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버프 테이블 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element_Status_Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태 이상 표시명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP 소모 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스피드 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>받피증</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>속성 게이지 저항 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table_Element_Status</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -725,8 +2128,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -869,7 +2273,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -961,6 +2365,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2893,9 +4303,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="동우 제" id="{5D12DBE9-E029-4CE0-B5DC-BBBD2017EA93}" userId="b4acf424e0b596a4" providerId="Windows Live"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3159,28 +4567,6 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E3" dT="2025-10-21T11:39:35.49" personId="{5D12DBE9-E029-4CE0-B5DC-BBBD2017EA93}" id="{E8D9F2FE-E5E0-40C4-A56A-56D345786A22}">
-    <text xml:space="preserve">0: None
-1: 물리
-2: 화염
-3: 방사능
-4: 중력
-5: 공허
-6: 신성
-7: 물리+물리
-8: 화염+화염
-9: 방사능+방사능
-10: 중력+중력
-11: 공허+공허
-12: 신성+신성
-13: 카오스
-</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2">
@@ -3188,6 +4574,9 @@
   </sheetPr>
   <dimension ref="A2:E18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -3290,6 +4679,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="19"/>
       <c r="C14" t="s">
         <v>71</v>
       </c>
@@ -3445,10 +4835,10 @@
         <v>51</v>
       </c>
       <c r="O3" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q3" s="15" t="s">
         <v>40</v>
@@ -3642,24 +5032,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AK17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" style="30" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.375" style="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.875" style="30" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.375" style="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>79</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C1"/>
+      <c r="D1"/>
       <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>75</v>
       </c>
@@ -3673,17 +5068,15 @@
         <v>74</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>89</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="H2" s="22"/>
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
       <c r="K2" s="22"/>
@@ -3713,9 +5106,8 @@
       <c r="AI2" s="22"/>
       <c r="AJ2" s="22"/>
       <c r="AK2" s="22"/>
-      <c r="AL2" s="22"/>
     </row>
-    <row r="3" spans="1:38" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:37" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>56</v>
       </c>
@@ -3729,12 +5121,14 @@
         <v>56</v>
       </c>
       <c r="E3" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="G3" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="29"/>
       <c r="H3" s="29"/>
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
@@ -3765,9 +5159,8 @@
       <c r="AI3" s="29"/>
       <c r="AJ3" s="29"/>
       <c r="AK3" s="29"/>
-      <c r="AL3" s="29"/>
     </row>
-    <row r="4" spans="1:38" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:37" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>53</v>
       </c>
@@ -3781,7 +5174,7 @@
         <v>61</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F4" s="26"/>
       <c r="G4" s="26"/>
@@ -3815,27 +5208,28 @@
       <c r="AI4" s="26"/>
       <c r="AJ4" s="26"/>
       <c r="AK4" s="26"/>
-      <c r="AL4" s="26"/>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="24">
-        <f>(B5*10000000) + (C5*10000) + D5</f>
-        <v>300001001</v>
+        <f>(B5*1000000) + (C5*10000) + D5</f>
+        <v>40011000</v>
       </c>
       <c r="B5" s="24">
-        <v>30</v>
-      </c>
-      <c r="C5" s="24">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="C5" s="31">
+        <v>1</v>
       </c>
       <c r="D5" s="24">
-        <v>1001</v>
-      </c>
-      <c r="E5" s="24" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24">
+        <v>1</v>
+      </c>
+      <c r="G5" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
@@ -3866,25 +5260,28 @@
       <c r="AI5" s="25"/>
       <c r="AJ5" s="25"/>
       <c r="AK5" s="25"/>
-      <c r="AL5" s="25"/>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="24">
-        <f>(B6*10000000) + (C6*10000) + D6</f>
-        <v>300011002</v>
+        <f>(B6*1000000) + (C6*10000) + D6</f>
+        <v>40011001</v>
       </c>
       <c r="B6" s="24">
-        <v>30</v>
-      </c>
-      <c r="C6" s="24">
+        <v>40</v>
+      </c>
+      <c r="C6" s="31">
         <v>1</v>
       </c>
       <c r="D6" s="24">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E6" s="24"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
+      <c r="F6" s="24">
+        <v>2</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>87</v>
+      </c>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
@@ -3915,18 +5312,249 @@
       <c r="AI6" s="25"/>
       <c r="AJ6" s="25"/>
       <c r="AK6" s="25"/>
-      <c r="AL6" s="25"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A7" s="24">
+        <f t="shared" ref="A7:A17" si="0">(B7*1000000) + (C7*10000) + D7</f>
+        <v>40011002</v>
+      </c>
+      <c r="B7" s="24">
+        <v>40</v>
+      </c>
+      <c r="C7" s="32">
+        <v>1</v>
+      </c>
+      <c r="D7" s="30">
+        <v>1002</v>
+      </c>
+      <c r="F7" s="30">
+        <v>3</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A8" s="24">
+        <f t="shared" si="0"/>
+        <v>40011003</v>
+      </c>
+      <c r="B8" s="24">
+        <v>40</v>
+      </c>
+      <c r="C8" s="32">
+        <v>1</v>
+      </c>
+      <c r="D8" s="30">
+        <v>1003</v>
+      </c>
+      <c r="F8" s="30">
+        <v>4</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A9" s="24">
+        <f t="shared" si="0"/>
+        <v>40011004</v>
+      </c>
+      <c r="B9" s="24">
+        <v>40</v>
+      </c>
+      <c r="C9" s="32">
+        <v>1</v>
+      </c>
+      <c r="D9" s="30">
+        <v>1004</v>
+      </c>
+      <c r="F9" s="30">
+        <v>5</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A10" s="24">
+        <f t="shared" si="0"/>
+        <v>40011005</v>
+      </c>
+      <c r="B10" s="24">
+        <v>40</v>
+      </c>
+      <c r="C10" s="32">
+        <v>1</v>
+      </c>
+      <c r="D10" s="30">
+        <v>1005</v>
+      </c>
+      <c r="F10" s="30">
+        <v>6</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A11" s="24">
+        <f t="shared" si="0"/>
+        <v>40022000</v>
+      </c>
+      <c r="B11" s="24">
+        <v>40</v>
+      </c>
+      <c r="C11" s="32">
+        <v>2</v>
+      </c>
+      <c r="D11" s="30">
+        <v>2000</v>
+      </c>
+      <c r="F11" s="30">
+        <v>1</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A12" s="24">
+        <f t="shared" si="0"/>
+        <v>40022001</v>
+      </c>
+      <c r="B12" s="24">
+        <v>40</v>
+      </c>
+      <c r="C12" s="32">
+        <v>2</v>
+      </c>
+      <c r="D12" s="30">
+        <v>2001</v>
+      </c>
+      <c r="F12" s="30">
+        <v>7</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A13" s="24">
+        <f t="shared" si="0"/>
+        <v>40022002</v>
+      </c>
+      <c r="B13" s="24">
+        <v>40</v>
+      </c>
+      <c r="C13" s="32">
+        <v>2</v>
+      </c>
+      <c r="D13" s="30">
+        <v>2002</v>
+      </c>
+      <c r="F13" s="30">
+        <v>3</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A14" s="24">
+        <f t="shared" si="0"/>
+        <v>40022003</v>
+      </c>
+      <c r="B14" s="24">
+        <v>40</v>
+      </c>
+      <c r="C14" s="32">
+        <v>2</v>
+      </c>
+      <c r="D14" s="30">
+        <v>2003</v>
+      </c>
+      <c r="F14" s="30">
+        <v>4</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A15" s="24">
+        <f t="shared" si="0"/>
+        <v>40022004</v>
+      </c>
+      <c r="B15" s="24">
+        <v>40</v>
+      </c>
+      <c r="C15" s="32">
+        <v>2</v>
+      </c>
+      <c r="D15" s="30">
+        <v>2004</v>
+      </c>
+      <c r="F15" s="30">
+        <v>8</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A16" s="24">
+        <f t="shared" si="0"/>
+        <v>40022005</v>
+      </c>
+      <c r="B16" s="24">
+        <v>40</v>
+      </c>
+      <c r="C16" s="32">
+        <v>2</v>
+      </c>
+      <c r="D16" s="30">
+        <v>2005</v>
+      </c>
+      <c r="F16" s="30">
+        <v>6</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="24">
+        <f t="shared" si="0"/>
+        <v>40033000</v>
+      </c>
+      <c r="B17" s="24">
+        <v>40</v>
+      </c>
+      <c r="C17" s="32">
+        <v>3</v>
+      </c>
+      <c r="D17" s="30">
+        <v>3000</v>
+      </c>
+      <c r="F17" s="30">
+        <v>9</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E6" xr:uid="{BB0C1B74-2EBF-45D5-904D-A808855FF3F4}">
-      <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F1048576" xr:uid="{5F3CB115-75D3-4E18-94B1-D5ED884AD77E}">
+      <formula1>"0,1,2,3,4,5,6,7,8,9"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">

--- a/Assets/Data/DataTable/09_Element_Status.xlsx
+++ b/Assets/Data/DataTable/09_Element_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D130599-E440-456B-94AD-7F93C13F8068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF2B9D0-8206-4BB7-ABEF-F667FBBBF3C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
@@ -2128,9 +2128,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="179" formatCode="00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -2273,7 +2272,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2367,10 +2366,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4300,10 +4296,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5035,10 +5027,10 @@
   <dimension ref="A1:AK17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="30" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="31" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.375" style="30" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.875" style="30" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.375" style="30" bestFit="1" customWidth="1"/>
@@ -5048,6 +5040,7 @@
       <c r="A1" t="s">
         <v>93</v>
       </c>
+      <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
       <c r="E1"/>
@@ -5109,16 +5102,16 @@
     </row>
     <row r="3" spans="1:37" s="27" customFormat="1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>68</v>
@@ -5210,17 +5203,17 @@
       <c r="AK4" s="26"/>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A5" s="24">
+      <c r="A5" s="25">
         <f>(B5*1000000) + (C5*10000) + D5</f>
         <v>40011000</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <v>40</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="25">
         <v>1</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>1000</v>
       </c>
       <c r="E5" s="24"/>
@@ -5262,17 +5255,17 @@
       <c r="AK5" s="25"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" s="24">
+      <c r="A6" s="25">
         <f>(B6*1000000) + (C6*10000) + D6</f>
         <v>40011001</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="25">
         <v>40</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="25">
         <v>1</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>1001</v>
       </c>
       <c r="E6" s="24"/>
@@ -5314,17 +5307,17 @@
       <c r="AK6" s="25"/>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="25">
         <f t="shared" ref="A7:A17" si="0">(B7*1000000) + (C7*10000) + D7</f>
         <v>40011002</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="25">
         <v>40</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="31">
         <v>1</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>1002</v>
       </c>
       <c r="F7" s="30">
@@ -5335,17 +5328,17 @@
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A8" s="24">
+      <c r="A8" s="25">
         <f t="shared" si="0"/>
         <v>40011003</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <v>40</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="31">
         <v>1</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>1003</v>
       </c>
       <c r="F8" s="30">
@@ -5356,17 +5349,17 @@
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A9" s="24">
+      <c r="A9" s="25">
         <f t="shared" si="0"/>
         <v>40011004</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <v>40</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="31">
         <v>1</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>1004</v>
       </c>
       <c r="F9" s="30">
@@ -5377,17 +5370,17 @@
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A10" s="24">
+      <c r="A10" s="25">
         <f t="shared" si="0"/>
         <v>40011005</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="25">
         <v>40</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="31">
         <v>1</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>1005</v>
       </c>
       <c r="F10" s="30">
@@ -5398,17 +5391,17 @@
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
+      <c r="A11" s="25">
         <f t="shared" si="0"/>
         <v>40022000</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <v>40</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="31">
         <v>2</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>2000</v>
       </c>
       <c r="F11" s="30">
@@ -5419,17 +5412,17 @@
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A12" s="24">
+      <c r="A12" s="25">
         <f t="shared" si="0"/>
         <v>40022001</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="25">
         <v>40</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="31">
         <v>2</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>2001</v>
       </c>
       <c r="F12" s="30">
@@ -5440,17 +5433,17 @@
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A13" s="24">
+      <c r="A13" s="25">
         <f t="shared" si="0"/>
         <v>40022002</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="25">
         <v>40</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="31">
         <v>2</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>2002</v>
       </c>
       <c r="F13" s="30">
@@ -5461,17 +5454,17 @@
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A14" s="24">
+      <c r="A14" s="25">
         <f t="shared" si="0"/>
         <v>40022003</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="25">
         <v>40</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="31">
         <v>2</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>2003</v>
       </c>
       <c r="F14" s="30">
@@ -5482,17 +5475,17 @@
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A15" s="24">
+      <c r="A15" s="25">
         <f t="shared" si="0"/>
         <v>40022004</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="25">
         <v>40</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="31">
         <v>2</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>2004</v>
       </c>
       <c r="F15" s="30">
@@ -5503,17 +5496,17 @@
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A16" s="24">
+      <c r="A16" s="25">
         <f t="shared" si="0"/>
         <v>40022005</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="25">
         <v>40</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="31">
         <v>2</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>2005</v>
       </c>
       <c r="F16" s="30">
@@ -5524,17 +5517,17 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="24">
+      <c r="A17" s="25">
         <f t="shared" si="0"/>
         <v>40033000</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="25">
         <v>40</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="31">
         <v>3</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>3000</v>
       </c>
       <c r="F17" s="30">
